--- a/artfynd/A 47911-2023 artfynd.xlsx
+++ b/artfynd/A 47911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557365</v>
+        <v>121557364</v>
       </c>
       <c r="B2" t="n">
-        <v>74698</v>
+        <v>5192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384311</v>
+        <v>384312</v>
       </c>
       <c r="R2" t="n">
         <v>6418500</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557364</v>
+        <v>121557365</v>
       </c>
       <c r="B3" t="n">
-        <v>5192</v>
+        <v>74698</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384312</v>
+        <v>384311</v>
       </c>
       <c r="R3" t="n">
         <v>6418500</v>

--- a/artfynd/A 47911-2023 artfynd.xlsx
+++ b/artfynd/A 47911-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121557365</v>
       </c>
       <c r="B3" t="n">
-        <v>74698</v>
+        <v>74699</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47911-2023 artfynd.xlsx
+++ b/artfynd/A 47911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557364</v>
+        <v>121557365</v>
       </c>
       <c r="B2" t="n">
-        <v>5192</v>
+        <v>74699</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384312</v>
+        <v>384311</v>
       </c>
       <c r="R2" t="n">
         <v>6418500</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557365</v>
+        <v>121557364</v>
       </c>
       <c r="B3" t="n">
-        <v>74699</v>
+        <v>5192</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384311</v>
+        <v>384312</v>
       </c>
       <c r="R3" t="n">
         <v>6418500</v>

--- a/artfynd/A 47911-2023 artfynd.xlsx
+++ b/artfynd/A 47911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557365</v>
+        <v>121557364</v>
       </c>
       <c r="B2" t="n">
-        <v>74699</v>
+        <v>5192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384311</v>
+        <v>384312</v>
       </c>
       <c r="R2" t="n">
         <v>6418500</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557364</v>
+        <v>121557365</v>
       </c>
       <c r="B3" t="n">
-        <v>5192</v>
+        <v>74699</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384312</v>
+        <v>384311</v>
       </c>
       <c r="R3" t="n">
         <v>6418500</v>

--- a/artfynd/A 47911-2023 artfynd.xlsx
+++ b/artfynd/A 47911-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121557364</v>
       </c>
       <c r="B2" t="n">
-        <v>5192</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121557365</v>
       </c>
       <c r="B3" t="n">
-        <v>74699</v>
+        <v>74706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 47911-2023 artfynd.xlsx
+++ b/artfynd/A 47911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557364</v>
+        <v>121557365</v>
       </c>
       <c r="B2" t="n">
-        <v>5193</v>
+        <v>74706</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>6439</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384312</v>
+        <v>384311</v>
       </c>
       <c r="R2" t="n">
         <v>6418500</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557365</v>
+        <v>121557364</v>
       </c>
       <c r="B3" t="n">
-        <v>74706</v>
+        <v>5193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6439</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384311</v>
+        <v>384312</v>
       </c>
       <c r="R3" t="n">
         <v>6418500</v>

--- a/artfynd/A 47911-2023 artfynd.xlsx
+++ b/artfynd/A 47911-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557365</v>
+        <v>121557364</v>
       </c>
       <c r="B2" t="n">
-        <v>74706</v>
+        <v>5193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>105930</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384311</v>
+        <v>384312</v>
       </c>
       <c r="R2" t="n">
         <v>6418500</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557364</v>
+        <v>121557365</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
+        <v>74706</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384312</v>
+        <v>384311</v>
       </c>
       <c r="R3" t="n">
         <v>6418500</v>

--- a/artfynd/A 47911-2023 artfynd.xlsx
+++ b/artfynd/A 47911-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121557365</v>
+        <v>121557362</v>
       </c>
       <c r="B2" t="n">
-        <v>74706</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>384311</v>
+        <v>384243</v>
       </c>
       <c r="R2" t="n">
-        <v>6418500</v>
+        <v>6418568</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121557364</v>
+        <v>121557365</v>
       </c>
       <c r="B3" t="n">
-        <v>5193</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6439</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,7 +811,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>384312</v>
+        <v>384311</v>
       </c>
       <c r="R3" t="n">
         <v>6418500</v>
@@ -880,6 +870,208 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>FNT0024 Borgstena</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121557366</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Borgstena, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>384353</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6418524</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Borgstena</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>FNT0024 Borgstena</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121557364</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Borgstena, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>384312</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6418500</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Borgstena</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Lundin</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Robin Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>FNT0024 Borgstena</t>
         </is>

--- a/artfynd/A 47911-2023 artfynd.xlsx
+++ b/artfynd/A 47911-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>FNT0024 Borgstena</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121557362</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>FNT0024 Borgstena</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121557365</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>FNT0024 Borgstena</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121557366</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>FNT0024 Borgstena</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121557364</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>